--- a/assets/umumiy_hisobot_shabloni.xlsx
+++ b/assets/umumiy_hisobot_shabloni.xlsx
@@ -1,137 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A69A77-8A7B-46EE-873E-813037AD6B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>karobkalani kilosi</t>
-  </si>
-  <si>
-    <t>qoshilgan karobka</t>
-  </si>
-  <si>
-    <t>Toza yuk</t>
-  </si>
-  <si>
-    <t>karobka 1kg uchun</t>
-  </si>
-  <si>
-    <t>karobka</t>
-  </si>
-  <si>
-    <t>mandarin</t>
-  </si>
-  <si>
-    <t>akb</t>
-  </si>
-  <si>
-    <t>jet</t>
-  </si>
-  <si>
-    <t>xabib</t>
-  </si>
-  <si>
-    <t>navo</t>
-  </si>
-  <si>
-    <t>izi</t>
-  </si>
-  <si>
-    <t>jon</t>
-  </si>
-  <si>
-    <t>one</t>
-  </si>
-  <si>
-    <t>redwing</t>
-  </si>
-  <si>
-    <t>triton</t>
-  </si>
-  <si>
-    <t>top</t>
-  </si>
-  <si>
-    <t>uzt</t>
-  </si>
-  <si>
-    <t>M174</t>
-  </si>
-  <si>
-    <t>29,06,2026</t>
-  </si>
-  <si>
-    <t>M233</t>
-  </si>
-  <si>
-    <t>umumiy  og'irligi:</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="204"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="204"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39991454817346722"/>
+        <fgColor theme="4" tint="0.3999145481734672"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -175,31 +101,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -460,302 +445,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H129"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="26.81640625" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="9" width="8.08984375" customWidth="1"/>
-    <col min="10" max="10" width="16.1796875" customWidth="1"/>
+    <col width="15.6328125" customWidth="1" min="1" max="1"/>
+    <col width="11.1796875" customWidth="1" min="2" max="2"/>
+    <col width="16.54296875" customWidth="1" min="4" max="4"/>
+    <col width="26.81640625" customWidth="1" min="5" max="5"/>
+    <col width="17.90625" customWidth="1" min="6" max="6"/>
+    <col width="16.1796875" customWidth="1" min="7" max="7"/>
+    <col width="17.36328125" customWidth="1" min="8" max="8"/>
+    <col width="8.08984375" customWidth="1" min="9" max="9"/>
+    <col width="16.1796875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>karobkalani kilosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>707.72</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B2" s="2" t="n"/>
       <c r="C2" s="2">
         <f>SUM(A:A)</f>
-        <v>707.72</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4">
+        <v/>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>qoshilgan karobka</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>umumiy  og'irligi:</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>29,06,2026</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Toza yuk</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>karobka 1kg uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>karobka</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6" t="s">
-        <v>19</v>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>M233</t>
+        </is>
       </c>
       <c r="G3" s="5">
         <f>C2-C9-C13-C3-C14</f>
-        <v>510.43999999999994</v>
+        <v/>
       </c>
       <c r="H3" s="7">
         <f>C3/G3</f>
-        <v>8.6200141054776275E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>mandarin</t>
+        </is>
       </c>
       <c r="C4" s="6">
         <f>G3-C5-C6-C8-C7-C11-C10-C12-C15</f>
-        <v>203.61999999999995</v>
+        <v/>
       </c>
       <c r="D4" s="7">
         <f>C4*H3</f>
-        <v>17.552072721573541</v>
-      </c>
-      <c r="E4" s="7">
+        <v/>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>221.18</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>akb</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>40.56</v>
       </c>
       <c r="D5" s="7">
         <f>C5*H3</f>
-        <v>3.496277721181726</v>
+        <v/>
       </c>
       <c r="E5" s="7">
         <f>C5+D5</f>
-        <v>44.056277721181729</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
+        <v/>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>27.9</v>
       </c>
       <c r="D6" s="7">
         <f>C6*$H$3</f>
-        <v>2.4049839354282581</v>
+        <v/>
       </c>
       <c r="E6" s="7">
-        <f t="shared" ref="E6:E15" si="0">C6+D6</f>
-        <v>30.304983935428258</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5">
+        <f>C6+D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>xabib</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>130.18</v>
       </c>
       <c r="D7" s="7">
         <f>C7*$H$3</f>
-        <v>11.221534362510775</v>
+        <v/>
       </c>
       <c r="E7" s="7">
-        <f t="shared" si="0"/>
-        <v>141.40153436251077</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
+        <f>C7+D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>navo</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>32.64</v>
       </c>
       <c r="D8" s="7">
         <f>C8*$H$3</f>
-        <v>2.8135726040278977</v>
+        <v/>
       </c>
       <c r="E8" s="7">
-        <f t="shared" si="0"/>
-        <v>35.453572604027897</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5">
+        <f>C8+D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>izi</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>106.96</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="7">
-        <f t="shared" si="0"/>
-        <v>106.96</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5">
+        <f>C9+D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>jon</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>25.66</v>
       </c>
       <c r="D10" s="7">
         <f>C10*$H$3</f>
-        <v>2.211895619465559</v>
+        <v/>
       </c>
       <c r="E10" s="7">
-        <f t="shared" si="0"/>
-        <v>27.871895619465558</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="5">
+        <f>C10+D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>27.68</v>
       </c>
       <c r="D11" s="7">
         <f>C11*$H$3</f>
-        <v>2.3860199043962074</v>
+        <v/>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="0"/>
-        <v>30.066019904396207</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="5">
+        <f>C11+D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>redwing</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>21.84</v>
       </c>
       <c r="D12" s="7">
         <f>C12*$H$3</f>
-        <v>1.8826110806363139</v>
+        <v/>
       </c>
       <c r="E12" s="7">
-        <f t="shared" si="0"/>
-        <v>23.722611080636312</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="5">
+        <f>C12+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>triton</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>46.32</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="7">
-        <f t="shared" si="0"/>
-        <v>46.32</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+        <f>C13+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
       <c r="E14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="8">
+        <f>C14+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>uzt</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>0.36</v>
       </c>
       <c r="D15" s="7">
         <f>C15*$H$3</f>
-        <v>3.1032050779719458E-2</v>
+        <v/>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="0"/>
-        <v>0.39103205077971942</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="C16" s="1"/>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="10"/>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="10"/>
+        <f>C15+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="1" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <pageSetup orientation="portrait" paperSize="256" horizontalDpi="203" verticalDpi="203"/>
 </worksheet>
 </file>
--- a/assets/umumiy_hisobot_shabloni.xlsx
+++ b/assets/umumiy_hisobot_shabloni.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -678,7 +678,7 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>oneway</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
